--- a/src/attributions/attributions_ig_traj_441.xlsx
+++ b/src/attributions/attributions_ig_traj_441.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2743115080938763</v>
+        <v>0.08077026581570916</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,13 +1011,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01752996409389752</v>
+        <v>-0.01294245509686282</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1290090432158836</v>
+        <v>-0.02563749867644909</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -1029,25 +1029,25 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1896620531747152</v>
+        <v>0.1125409032228731</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.006678067651017304</v>
+        <v>-0.03003542979184579</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.09102176666821046</v>
+        <v>-0.01329228564988065</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1056,49 +1056,49 @@
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.002507764033312028</v>
+        <v>0.02432085357489486</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.1216333004285383</v>
+        <v>-0.02128689674079915</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.05311079682315385</v>
+        <v>-0.003278264168026419</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.761522365711898e-11</v>
+        <v>-1.237176348748949e-11</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.595464399012346e-11</v>
+        <v>-4.479842153952651e-11</v>
       </c>
       <c r="AG2" t="n">
-        <v>-8.354591643159853e-12</v>
+        <v>-3.430803409469376e-13</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05120216586079463</v>
+        <v>0.04221261702576747</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,10 +1119,10 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.04677984130800337</v>
+        <v>0.01330273550284883</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.1682298124567096</v>
+        <v>-0.02574589530457324</v>
       </c>
       <c r="AQ2" t="n">
         <v>-0</v>
@@ -1134,28 +1134,28 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4634689099043804</v>
+        <v>0.1560233461603376</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.02600974164591208</v>
+        <v>-0.05100648160335998</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.1671490162856555</v>
+        <v>-0.04801085061287119</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.04298925702074981</v>
+        <v>-0.001314812398428934</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,64 +1173,64 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.02123230578245329</v>
+        <v>-0.01018203718589103</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.01922352272820982</v>
+        <v>-0.003981131720797995</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.181203274144081</v>
+        <v>-0.00332489773641013</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.08426255242815775</v>
+        <v>0.04812181985594832</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.03123332524595517</v>
+        <v>0.005120009938979288</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2140543596906546</v>
+        <v>0.1142664189457389</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.04411940047012342</v>
+        <v>-0.006567402307716463</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.01388962330631366</v>
+        <v>-0.03449960260875576</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
@@ -1245,46 +1245,46 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.09771213223954851</v>
+        <v>-0.0584490704073104</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.03062343194820516</v>
+        <v>0.006776348519680876</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.08338675673836668</v>
+        <v>0.03612994691841291</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.0192197420920768</v>
+        <v>-0.06289885652853307</v>
       </c>
       <c r="CO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.0245133408172032</v>
+        <v>0.03481032967809823</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.1082006264265352</v>
+        <v>0.04163642462594148</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,58 +1293,58 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.06492440065907977</v>
+        <v>-0.05471168514363196</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.02761830426653996</v>
+        <v>0.006098893083585472</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.09429309574617928</v>
+        <v>0.0382864673234037</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.009917188142163084</v>
+        <v>-0.009685771641820417</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01171564627735392</v>
+        <v>-0.01402311753798886</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.008389245862603052</v>
+        <v>0.01938582224442088</v>
       </c>
       <c r="DK2" t="n">
         <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
         <v>0</v>
@@ -1353,19 +1353,19 @@
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.04761297452225392</v>
+        <v>-0.03330397987288317</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.07672590289873633</v>
+        <v>0.01873489223806415</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.07092922562847516</v>
+        <v>0.0007449642848606026</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1380,34 +1380,34 @@
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.06410190591717878</v>
+        <v>0.03214358607754589</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03042189041904364</v>
+        <v>0.005960990397277846</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0.04467982636348111</v>
+        <v>-0.06965900645917415</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.03007011392934795</v>
+        <v>-0.01182937908705282</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
@@ -1416,37 +1416,37 @@
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.002865124287265554</v>
+        <v>-0.0102292187052421</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.05343499655567275</v>
+        <v>0.02172483161991549</v>
       </c>
       <c r="EL2" t="n">
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.0854521102741999</v>
+        <v>-0.02606871460297433</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.06136616790804077</v>
+        <v>-0.02734982924160702</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.1894485614312381</v>
+        <v>0.03004678529320428</v>
       </c>
       <c r="EU2" t="n">
         <v>-0</v>
@@ -1455,40 +1455,40 @@
         <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.06118579435631016</v>
+        <v>-0.0619994497810013</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
         <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.02123551304913026</v>
+        <v>-0.002533841822149727</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.08786336939117344</v>
+        <v>0.03342758362642397</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.04748600792208877</v>
+        <v>-0.03642036388705566</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
@@ -1497,37 +1497,37 @@
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.05438257677469473</v>
+        <v>0.0142760319031806</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.003680049134297337</v>
+        <v>0.00220292894785761</v>
       </c>
       <c r="FM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.08523670965876222</v>
+        <v>-0.006913554037863933</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.06726665050117556</v>
+        <v>0.001960464989522332</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.00811531285891794</v>
+        <v>-0.001452585979193034</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
@@ -1536,16 +1536,16 @@
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.05681257433684641</v>
+        <v>-0.0178580328475183</v>
       </c>
       <c r="GA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB2" t="n">
         <v>-0</v>
@@ -1554,13 +1554,13 @@
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0.06131407169778497</v>
+        <v>0.01798329330040753</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
         <v>0</v>
@@ -1571,22 +1571,22 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01254751349172637</v>
+        <v>-0.0009283142420477869</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1189495039802701</v>
+        <v>0.01182602969442543</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.03989846364054393</v>
+        <v>-0.01824936787979095</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -1595,100 +1595,100 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.05544948658776652</v>
+        <v>-0.003112686830188585</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1753649017526675</v>
+        <v>0.01003714117996499</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02564899427495532</v>
+        <v>-0.01670603531364613</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.056190105244269</v>
+        <v>-0.0001074069944380935</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06989908184052281</v>
+        <v>0.01209672553458769</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01258743395630189</v>
+        <v>0.00404557483671512</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.03362786049590677</v>
+        <v>-0.009521925790160446</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.009065777062096776</v>
+        <v>0.0005406297023450289</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.576309582927744e-11</v>
+        <v>-1.852302500506845e-11</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002363952999998976</v>
+        <v>-0.01513009854381047</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.06062736982374611</v>
+        <v>0.01593539510633358</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.02752295908452909</v>
+        <v>-0.003120253270502335</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1697,25 +1697,25 @@
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.1154916068740182</v>
+        <v>-0.0225498787316839</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1005547335964163</v>
+        <v>0.03734866032584279</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1817663703775287</v>
+        <v>-0.03735525857068782</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
@@ -1736,13 +1736,13 @@
         <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.009159648298634819</v>
+        <v>0.0003966114558114356</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.01315735121754001</v>
+        <v>-0.01227465087178735</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01115624759828031</v>
+        <v>-0.01196253985430001</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,49 +1754,49 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.02950776523106696</v>
+        <v>0.005382745876548574</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.06625095087877123</v>
+        <v>0.0297811448436138</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.06849743769361277</v>
+        <v>0.03700380182214601</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.1093605303596395</v>
+        <v>-0.001540580597873858</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1210209402506181</v>
+        <v>0.02602006617422839</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1092296081745087</v>
+        <v>0.0003934313149074308</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1805,7 +1805,7 @@
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -1817,19 +1817,19 @@
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.04862391619019686</v>
+        <v>0.01019698003662915</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0557791638982168</v>
+        <v>0.003974709626232037</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.002907508122991026</v>
+        <v>0.005561903579116302</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
@@ -1841,28 +1841,28 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.02171324639502373</v>
+        <v>-0.001130640193069934</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.02369688048980582</v>
+        <v>0.01616511454815064</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.05804308375597202</v>
+        <v>0.02866040853158743</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
         <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
         <v>-0</v>
@@ -1871,25 +1871,25 @@
         <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0369500220741209</v>
+        <v>0.006954815480467956</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.05668275985499761</v>
+        <v>0.002777719298672397</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.008035514211187349</v>
+        <v>0.008477984820420441</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -1898,67 +1898,67 @@
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.01705751296851888</v>
+        <v>0.004671730539411847</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.04319543173211763</v>
+        <v>-0.01424417749889241</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.003714694146988855</v>
+        <v>0.001803823280493877</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
         <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.004570419416753462</v>
+        <v>-0.004485854088485663</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.01579298445261038</v>
+        <v>-0.01258601541810652</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.02980784342543822</v>
+        <v>0.02501837725644156</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.0005768233288189662</v>
+        <v>-0.02178397042564851</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.04111018938813918</v>
+        <v>-0.008102343230826184</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.04405065660329108</v>
+        <v>-0.01483727115363042</v>
       </c>
       <c r="EB3" t="n">
         <v>-0</v>
@@ -1967,10 +1967,10 @@
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
         <v>0</v>
@@ -1979,19 +1979,19 @@
         <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.06426833572712112</v>
+        <v>-0.002859007003898484</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0662979687946296</v>
+        <v>0.0009378457526238661</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0239801080405099</v>
+        <v>-0.004977061789506756</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,31 +2000,31 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
         <v>-0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.03120878657616924</v>
+        <v>-0.003809835396911014</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0.02980944059919468</v>
+        <v>-0.002609619246766426</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.01236330595243111</v>
+        <v>0.01377572290495475</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX3" t="n">
         <v>0</v>
@@ -2033,40 +2033,40 @@
         <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.03734676030710679</v>
+        <v>0.005342214411510279</v>
       </c>
       <c r="FA3" t="n">
-        <v>-0.05603529873992402</v>
+        <v>-0.001358703614770268</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.002731617069391279</v>
+        <v>0.007904626955298638</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.04168713505694301</v>
+        <v>0.01021069220961661</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.007402947699181521</v>
+        <v>0.008764197883975092</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.01752036718788693</v>
+        <v>-0.02749428532521471</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
@@ -2075,25 +2075,25 @@
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.009199430866072679</v>
+        <v>0.0003372502505331237</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.003289070895095073</v>
+        <v>0.0008344545098187793</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.02619930551981697</v>
+        <v>0.01840654130913709</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2102,22 +2102,22 @@
         <v>0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.003480763919535976</v>
+        <v>-0.001521393919083219</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.03790513836758912</v>
+        <v>-0.02035831114130728</v>
       </c>
       <c r="GC3" t="n">
         <v>0</v>
@@ -2709,76 +2709,76 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07710138960658418</v>
+        <v>0.1161394201519243</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0592934649980321</v>
+        <v>-0.03410180197463717</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.03082085100794316</v>
+        <v>-0.03809875056089151</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04570815919397022</v>
+        <v>0.1757384722581325</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.05559042536858964</v>
+        <v>-0.07604841824624617</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.03664691208922091</v>
+        <v>-0.04531733195301886</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01476876869966069</v>
+        <v>0.0764687873683467</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01654505632304664</v>
+        <v>-0.03907818920661758</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02031878686217674</v>
+        <v>0.02600650657197913</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2790,19 +2790,19 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01374172609489367</v>
+        <v>-0.02153791065801643</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.002976368366179147</v>
+        <v>-0.02339453667908659</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.00154956834833887</v>
+        <v>0.006376043227555335</v>
       </c>
       <c r="AH5" t="n">
         <v>-0</v>
@@ -2811,52 +2811,52 @@
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02528431077362644</v>
+        <v>0.0286163871147699</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01878887870955002</v>
+        <v>-0.02728586960578488</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.006390065834809933</v>
+        <v>-0.03861184419041595</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.09850999644300303</v>
+        <v>0.276690839256556</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.07048378414987319</v>
+        <v>-0.1353675644957287</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.02894853848123702</v>
+        <v>-0.128377503583628</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,28 +2865,28 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.02097423860085062</v>
+        <v>-0.03017115423565566</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02033350587055423</v>
+        <v>-0.01825807491974981</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.006773115414709647</v>
+        <v>0.007182296619160127</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,55 +2895,55 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.04167734054206985</v>
+        <v>0.05717418220625626</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0178896841389973</v>
+        <v>0.08635957192713105</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01765942597364123</v>
+        <v>0.06308607595235889</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.04411140188489734</v>
+        <v>0.2006124505380221</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.0261577049449027</v>
+        <v>-0.03573028048247359</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.000137873520276579</v>
+        <v>-0.01847558621123575</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
@@ -2952,25 +2952,25 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01688322466454891</v>
+        <v>-0.05259543113609558</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01912402168003641</v>
+        <v>0.0312052413909738</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01939020179580972</v>
+        <v>0.0256831572972147</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,25 +2979,25 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.002735419814528794</v>
+        <v>-0.07637329278424125</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001310618773320322</v>
+        <v>0.07808431837662462</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.0105809246748544</v>
+        <v>-0.004661537176928546</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
         <v>0</v>
@@ -3006,25 +3006,25 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.007869337369024534</v>
+        <v>-0.04888867279163252</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01574040164101125</v>
+        <v>0.02263070003860308</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02602055264007925</v>
+        <v>0.03114302942203134</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,61 +3033,61 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.01533601115436029</v>
+        <v>-0.04843097598435273</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02620558934235264</v>
+        <v>-0.004747450232604839</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.004589393327685816</v>
+        <v>0.003113248757310741</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01489458407588808</v>
+        <v>-0.005869232969880059</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.02229499505045078</v>
+        <v>-0.0001324046734440395</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.02678313346265856</v>
+        <v>-0.01178506719798565</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01151293591685486</v>
+        <v>0.05718243536110411</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03219920600631691</v>
+        <v>-0.09587320744538141</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.000799059073130918</v>
+        <v>0.02104119667410272</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01121021065933306</v>
+        <v>0.01168370714244719</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.003157540870553318</v>
+        <v>-0.02219253851564371</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01915279225494401</v>
+        <v>0.007411938307853813</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.007428834688410854</v>
+        <v>-0.005019668748669575</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,16 +3150,16 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02117329997562055</v>
+        <v>-0.09631100293662644</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01104352086508034</v>
+        <v>0.01969273354280289</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
@@ -3168,7 +3168,7 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.003404034931334412</v>
+        <v>-0.05618793396304412</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,16 +3177,16 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01617631089462195</v>
+        <v>0.01203230972773534</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.02417614834488365</v>
+        <v>0.016805952728509</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,19 +3195,19 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02139003926436472</v>
+        <v>-0.03882928398055838</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03814093526810047</v>
+        <v>0.05694512933865339</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01269318243390147</v>
+        <v>0.004786629029941081</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3222,34 +3222,34 @@
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.003364954977012221</v>
+        <v>0.006580457977096192</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.0001814358105517493</v>
+        <v>-0.02132471258139589</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.01892183394703803</v>
+        <v>-0.06839529473171303</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0172990571606688</v>
+        <v>-0.05737776400755509</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3258,16 +3258,16 @@
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.00137655841245735</v>
+        <v>0.05143185218007416</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2844318628154626</v>
+        <v>0.211985735818394</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1098743301142869</v>
+        <v>-0.08258137857372908</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02248620957256975</v>
+        <v>0.01328590414228812</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,22 +3305,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2577031142972308</v>
+        <v>0.2514350634452777</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1325088040230284</v>
+        <v>-0.1122272642215672</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.08716244546388285</v>
+        <v>-0.00724837868423726</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,76 +3332,76 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1001422575645046</v>
+        <v>0.07551812761478663</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.03671398225704103</v>
+        <v>-0.03788832195916397</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0654465237425027</v>
+        <v>-0.05882124743802111</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.04648218195504</v>
+        <v>-0.0201734307913567</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.001386295482526571</v>
+        <v>-0.0325247255790161</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001028169894792358</v>
+        <v>-0.001085348860896964</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.03956268389346618</v>
+        <v>0.1027927186335985</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.04567381635873553</v>
+        <v>-0.04840328248800564</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01181494765947292</v>
+        <v>0.05493451078386974</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,25 +3410,25 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.3867913936655016</v>
+        <v>0.2551206771576999</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.003746838920987292</v>
+        <v>-0.06021222292154151</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.2061717612448196</v>
+        <v>-0.07067276129080989</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3440,16 +3440,16 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.008326607217299246</v>
+        <v>-0.01317425766658943</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.04048104884718543</v>
+        <v>-0.02901566439787782</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.07592555751745683</v>
+        <v>-0.01754199162137065</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,22 +3467,22 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0116922331877805</v>
+        <v>-0.008033213370564311</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.04941961958993465</v>
+        <v>-0.01453233886085489</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.05655814250328284</v>
+        <v>0.03354838719729268</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
@@ -3494,22 +3494,22 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.235838608980643</v>
+        <v>0.2015412846961568</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.01016982173616007</v>
+        <v>-0.0592643313024858</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.09764601883574001</v>
+        <v>-0.02939447697102445</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,19 +3521,19 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.08568224373246545</v>
+        <v>-0.09404842278865294</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01739922525702181</v>
+        <v>0.07332894444750745</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.01400547110548966</v>
+        <v>-0.02610391990001537</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
         <v>-0</v>
@@ -3548,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.04743206961735517</v>
+        <v>-0.0667758576155143</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.07970023789240654</v>
+        <v>0.1421134395864473</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.1780141759118013</v>
+        <v>0.03201969186506635</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3569,28 +3569,28 @@
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.07375137262751513</v>
+        <v>-0.08616104544145249</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.02313769784380983</v>
+        <v>0.07534597626975924</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.01402095684498433</v>
+        <v>-0.01593410440630358</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
@@ -3602,19 +3602,19 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.04239303702054946</v>
+        <v>-0.0639395846912145</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.01959941344120823</v>
+        <v>0.009823481168435922</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.01379336953219107</v>
+        <v>-0.04733567611072687</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
         <v>-0</v>
@@ -3626,22 +3626,22 @@
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.06829553357045939</v>
+        <v>-0.06422985613180487</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.02985894439814878</v>
+        <v>0.05880161106089628</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.05946351841557498</v>
+        <v>-0.01972746083878944</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3653,79 +3653,79 @@
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.03812324827954588</v>
+        <v>0.03946871775561388</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.01977567894439812</v>
+        <v>-0.04744878921027058</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.04134277043762103</v>
+        <v>0.0471172653566773</v>
       </c>
       <c r="EB6" t="n">
         <v>0</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.05073216386694406</v>
+        <v>-0.06825953085860073</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.04195045849544903</v>
+        <v>0.05447607452360693</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.04695776606162186</v>
+        <v>-0.01187105793437727</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.06671586363843154</v>
+        <v>-0.02519774973452734</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.02797783363694842</v>
+        <v>0.002487137728226333</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.005112310950050408</v>
+        <v>-0.009019122408944364</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,25 +3734,25 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0842828986269277</v>
+        <v>-0.1027349486469313</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.03573213583626421</v>
+        <v>0.07860010344874466</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.02165239996111048</v>
+        <v>-0.0246752872077785</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
@@ -3764,25 +3764,25 @@
         <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.005028182511796274</v>
+        <v>-0.05791388726902776</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.05765469306068702</v>
+        <v>0.05029952359205329</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.05235575472265181</v>
+        <v>-0.001711176992606162</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO6" t="n">
         <v>-0</v>
@@ -3791,40 +3791,40 @@
         <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.004737094071501808</v>
+        <v>0.003297953085269098</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.04983652987919214</v>
+        <v>0.03077705792112054</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.02609744076871311</v>
+        <v>-0.01433822300621203</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.03799009389361788</v>
+        <v>-0.08394052884481293</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.06101900478073304</v>
+        <v>0.02880752215249442</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
@@ -3836,10 +3836,10 @@
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,25 +3847,25 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1452946990942666</v>
+        <v>0.2567115508451135</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.007041043668583083</v>
+        <v>-0.005686148607425996</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.07834843064417112</v>
+        <v>-0.05988912968335414</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3874,25 +3874,25 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1148963113139924</v>
+        <v>0.3805281818899648</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.002568191796876374</v>
+        <v>-0.0614611176642155</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1090133793714032</v>
+        <v>-0.05060208801571617</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -3901,49 +3901,49 @@
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01536677134857771</v>
+        <v>0.06649360259586873</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.02467925202895664</v>
+        <v>-0.05455792698952775</v>
       </c>
       <c r="X7" t="n">
-        <v>0.005734553809758094</v>
+        <v>0.01673062232089503</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.01893722070176955</v>
+        <v>-0.009976524991144925</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.01175328391113499</v>
+        <v>-0.07847109985866139</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.007565244598927418</v>
+        <v>-0.03475594847096719</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
@@ -3955,19 +3955,19 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.006693731838250172</v>
+        <v>0.06637502103969346</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.03237704655684855</v>
+        <v>0.03302694734909691</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.02815100488614279</v>
+        <v>-0.02539343374816045</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0</v>
@@ -3979,28 +3979,28 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1257188238351603</v>
+        <v>0.3767160537000388</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.03882183044143388</v>
+        <v>-0.1373893709137139</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.07925508266631762</v>
+        <v>-0.05515660213003076</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>0</v>
@@ -4009,61 +4009,61 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.04432839845028674</v>
+        <v>0.008520441692125954</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.01196678929714049</v>
+        <v>-0.0387901857814731</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.0203087739960339</v>
+        <v>-0.03079929797510328</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0654511666129856</v>
+        <v>0.02670040589214907</v>
       </c>
       <c r="BN7" t="n">
         <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02385198385247353</v>
+        <v>0.05509697627679296</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.01148689410048041</v>
+        <v>-0.004049004626796598</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.06208116324015506</v>
+        <v>0.2554881266734981</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
@@ -4072,10 +4072,10 @@
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.00518052317426646</v>
+        <v>-0.02682187890461703</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.02904614736422339</v>
+        <v>-0.03815966336703472</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4084,67 +4084,67 @@
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.03485904182031496</v>
+        <v>-0.1098444853534705</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.004953114511919068</v>
+        <v>0.006579599131111395</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.03564948846319392</v>
+        <v>0.05594453468272321</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01158373643282451</v>
+        <v>-0.1882799064473744</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.01698017495831568</v>
+        <v>0.09948545591318775</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.02605197723867882</v>
+        <v>0.07109263211376533</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.02458018608907786</v>
+        <v>-0.1119675691241921</v>
       </c>
       <c r="CX7" t="n">
         <v>-0</v>
@@ -4153,16 +4153,16 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.005646837800130709</v>
+        <v>-0.01060993627960564</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0354581451806171</v>
+        <v>0.0520469476090327</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD7" t="n">
         <v>0</v>
@@ -4171,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.02397957652364528</v>
+        <v>-0.04577453574442274</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02074069244596599</v>
+        <v>-0.1367003822294791</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.004359673589193509</v>
+        <v>0.0224994330573997</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,31 +4192,31 @@
         <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.02160746670110682</v>
+        <v>-0.09915257267223372</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01035684517098687</v>
+        <v>0.05387868815458405</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.005645101122374551</v>
+        <v>-0.007188186804855353</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.02059595909823621</v>
+        <v>-0.0124201275136171</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
@@ -4234,10 +4234,10 @@
         <v>0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.0142750152779702</v>
+        <v>0.08105107734885146</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.02624826402372335</v>
+        <v>-0.1078337949108438</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4252,7 +4252,7 @@
         <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02314320489449101</v>
+        <v>-0.02123601165217517</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
@@ -4261,37 +4261,37 @@
         <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.005028097670422927</v>
+        <v>-0.05031749454935468</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.02123081181757024</v>
+        <v>0.02430052384181043</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.008209945022811263</v>
+        <v>-0.004594645909258692</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.004210018717703018</v>
+        <v>-0.08870376232135782</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.02592141748524442</v>
+        <v>0.04659596743546911</v>
       </c>
       <c r="EU7" t="n">
         <v>-0</v>
@@ -4306,73 +4306,73 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0250970624720597</v>
+        <v>-0.1254801547236861</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.001301642992304459</v>
+        <v>-0.01631756392919324</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.03815210308450429</v>
+        <v>0.04399205153320806</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.0009312168417003676</v>
+        <v>-0.166659615150877</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02425659023409844</v>
+        <v>0.1022716747951878</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.02423695923004239</v>
+        <v>0.01286641264503024</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0002285943718064047</v>
+        <v>0.001932743356747491</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.0007163156416172129</v>
+        <v>-0.00542035362053293</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.01887910933373645</v>
+        <v>-0.03199888739989271</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,31 +4381,31 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.009322380545003572</v>
+        <v>-0.02725596251317285</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.02644491083013127</v>
+        <v>0.004320742469379178</v>
       </c>
       <c r="GE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>0</v>
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.3736699439836315</v>
+        <v>0.260578885071462</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1111090442494771</v>
+        <v>-0.1180725213413954</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06972939572219503</v>
+        <v>-0.03787008692732969</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,19 +4443,19 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2741803697656536</v>
+        <v>0.2861987011680039</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1086343211332012</v>
+        <v>-0.1767872312615215</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.07587007001959879</v>
+        <v>-0.08118163386962955</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P8" t="n">
         <v>-0</v>
@@ -4470,70 +4470,70 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1073257933710293</v>
+        <v>0.07255949055179867</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.02742594692419606</v>
+        <v>-0.05446305183961782</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0391605792092602</v>
+        <v>-0.06528803802038902</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.05436192758026396</v>
+        <v>-0.04882154278152735</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.006213288000910096</v>
+        <v>-0.05812376107767864</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01784502302730625</v>
+        <v>-0.06607531660720592</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0429380405365526</v>
+        <v>0.1218004605768027</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.05192580534717805</v>
+        <v>-0.04462760891350588</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.05753196914089295</v>
+        <v>0.0686462450287207</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -4551,25 +4551,25 @@
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.4159785066481036</v>
+        <v>0.3441779717788283</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.02627152034215901</v>
+        <v>-0.08014925493097631</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0732902250624476</v>
+        <v>-0.1359250447019642</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.01289607907114811</v>
+        <v>-0.035977694695205</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.04580020400500418</v>
+        <v>-0.0210366744898917</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1073756151199869</v>
+        <v>-0.03461952221008272</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
@@ -4596,31 +4596,31 @@
         <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.04752874959572211</v>
+        <v>-0.0004940422450920595</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.05213149901093163</v>
+        <v>-0.002551157579756763</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1035631429896458</v>
+        <v>0.05170339026848187</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
         <v>-0</v>
@@ -4629,49 +4629,49 @@
         <v>-0</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.2070871295055775</v>
+        <v>0.2615636679089712</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.03355096022230637</v>
+        <v>-0.1065931521663205</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.03566733112169791</v>
+        <v>-0.05326377507176269</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.09691301453997864</v>
+        <v>-0.113614412417744</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.01277275637341894</v>
+        <v>0.07700025946578846</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01701594719042847</v>
+        <v>0.01204473950598159</v>
       </c>
       <c r="CI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ8" t="n">
         <v>-0</v>
@@ -4680,25 +4680,25 @@
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.001939199528956304</v>
+        <v>-0.1059177660304846</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.09441536577050862</v>
+        <v>0.1546546945724335</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.1069766176741129</v>
+        <v>0.05738150587023443</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
         <v>-0</v>
@@ -4707,25 +4707,25 @@
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.08576267887201537</v>
+        <v>-0.1076504616750549</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02820992177304668</v>
+        <v>0.08806218891849876</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.02760437353159043</v>
+        <v>0.009732569016452232</v>
       </c>
       <c r="DA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB8" t="n">
         <v>0</v>
@@ -4740,22 +4740,22 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.02456080213939923</v>
+        <v>-0.06841791250181262</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.0255899074429797</v>
+        <v>0.02795692115991846</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03556033547063503</v>
+        <v>-0.05259811646129335</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
@@ -4767,19 +4767,19 @@
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.03932537122585802</v>
+        <v>-0.04046163237030035</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.05990523221167709</v>
+        <v>0.0004266067190140261</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.06262593417186854</v>
+        <v>-0.0191060951204505</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4791,79 +4791,79 @@
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.02415998609982049</v>
+        <v>0.1124029504273153</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.004731324178139031</v>
+        <v>0.05260481260699411</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.0726309257012745</v>
+        <v>-0.04681004058076506</v>
       </c>
       <c r="EB8" t="n">
         <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
         <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.08060149747796154</v>
+        <v>-0.05468765966272697</v>
       </c>
       <c r="EH8" t="n">
         <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.02846258648066465</v>
+        <v>0.05162664328036631</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.05408122493806262</v>
+        <v>0.03419364689893844</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.05493272102814956</v>
+        <v>-0.04344794868912145</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.03784514726638923</v>
+        <v>0.07790766007698544</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.02232329686622774</v>
+        <v>-0.06513296426944946</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4872,46 +4872,46 @@
         <v>-0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.08245117972676837</v>
+        <v>-0.1242366672587818</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.02098579156083209</v>
+        <v>0.09521261143066424</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.01356111106783151</v>
+        <v>-0.005330176149197032</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02602992146503139</v>
+        <v>-0.03795236854287641</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0519464853993246</v>
+        <v>0.06975467978925143</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.05239538892586627</v>
+        <v>-0.01257603636469524</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
@@ -4923,61 +4923,61 @@
         <v>-0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>8.466370214392842e-05</v>
+        <v>0.0004087778447526459</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.03601085780486938</v>
+        <v>0.07263221644417615</v>
       </c>
       <c r="FT8" t="n">
-        <v>5.208333738372331e-05</v>
+        <v>-0.003945284103857665</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.001751769973497269</v>
+        <v>-0.09130109076787718</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.04496225973144782</v>
+        <v>0.0497581568116039</v>
       </c>
       <c r="GC8" t="n">
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8757358400654618</v>
+        <v>0.4403429855924919</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1739822999462084</v>
+        <v>0.1244588906419472</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6052980525206965</v>
+        <v>-0.3573275403602778</v>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,25 +5012,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7016243590570893</v>
+        <v>0.7181222349732124</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1666693418011055</v>
+        <v>0.02525456695787872</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7479677582627354</v>
+        <v>-0.3927443756946662</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1451387849260314</v>
+        <v>0.2220988734977141</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,52 +5048,52 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0592281027658556</v>
+        <v>-0.1940909272794008</v>
       </c>
       <c r="X9" t="n">
-        <v>0.02771201603258624</v>
+        <v>-0.03042306134382886</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1627531421057762</v>
+        <v>0.06293543913970813</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.07351613561396965</v>
+        <v>-0.3133987195488411</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.001224004008006532</v>
+        <v>-0.1959727216429111</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1988605125494959</v>
+        <v>0.1626272370159441</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.05325994772216466</v>
+        <v>0.008053306844531342</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.1543673859039075</v>
+        <v>-0.249861000962278</v>
       </c>
       <c r="AQ9" t="n">
         <v>-0</v>
@@ -5117,37 +5117,37 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.780955627497029</v>
+        <v>1.023123831738067</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.1905854617420649</v>
+        <v>-0.05912599473448602</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.5106360843688624</v>
+        <v>-0.2607892148252819</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.1598629162213758</v>
+        <v>-0.1165427248832331</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,64 +5156,64 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1891193138392337</v>
+        <v>-0.1751402486170377</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.1236609488946972</v>
+        <v>-0.2082273174326935</v>
       </c>
       <c r="BI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.19558314950627</v>
+        <v>0.197040228668892</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.06154458199384372</v>
+        <v>0.2118948681990397</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0.001465827215218763</v>
+        <v>-0.005450101236091302</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.4084437961544864</v>
+        <v>0.5737857596671685</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.1807611910570495</v>
+        <v>-0.0655362404611531</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.2857942354051501</v>
+        <v>-0.2408412590111305</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5228,49 +5228,49 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.1923155253277998</v>
+        <v>-0.2171628471686366</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.04238052656661087</v>
+        <v>0.01010027465048202</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.1727191447606748</v>
+        <v>0.1767904844139851</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.017762237474687</v>
+        <v>-0.5315221390241985</v>
       </c>
       <c r="CO9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP9" t="n">
         <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.07742937035808944</v>
+        <v>0.2636126232589538</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.0452642842253728</v>
+        <v>0.3433682480554994</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
         <v>-0</v>
@@ -5282,46 +5282,46 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.1615659671161713</v>
+        <v>-0.2117323220571365</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.03376175048949161</v>
+        <v>-0.05512531286808706</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.1908203413111675</v>
+        <v>0.162744136590544</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03711053544368546</v>
+        <v>-0.01788755370189976</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>-0.009889275010642986</v>
+        <v>-0.2264600710390211</v>
       </c>
       <c r="DJ9" t="n">
-        <v>-0.03693574437359947</v>
+        <v>0.02027571235977396</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
@@ -5330,40 +5330,40 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.03680603889925194</v>
+        <v>-0.04948465176344614</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.02617836966393604</v>
+        <v>-0.01087074367971267</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.001236345588553991</v>
+        <v>0.03347328884734276</v>
       </c>
       <c r="DT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW9" t="n">
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.05195343802956361</v>
+        <v>0.1396808858099517</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
@@ -5372,13 +5372,13 @@
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.009244594353104868</v>
+        <v>0.009777856486582323</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.04766372520199963</v>
+        <v>0.07834043156010098</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
         <v>0</v>
@@ -5387,37 +5387,37 @@
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.1267044799490827</v>
+        <v>-0.01118814548614527</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03938081492232988</v>
+        <v>-0.1518695308910662</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.2016464702588582</v>
+        <v>0.04270704406678973</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
         <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.08031520004278841</v>
+        <v>-0.03234290236055151</v>
       </c>
       <c r="EQ9" t="n">
         <v>0</v>
@@ -5426,91 +5426,91 @@
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02778648598307583</v>
+        <v>-0.1447206449678439</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.1128342582077246</v>
+        <v>0.1022275499346468</v>
       </c>
       <c r="EU9" t="n">
         <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.1497014728480349</v>
+        <v>-0.2364826994918215</v>
       </c>
       <c r="EZ9" t="n">
         <v>0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.04857416304001688</v>
+        <v>-0.08061522864279777</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.1614427342786538</v>
+        <v>0.1600396036627237</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.1035210991900925</v>
+        <v>-0.2489651956683366</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.02657560996278862</v>
+        <v>0.1574179283838816</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0.1367547473948276</v>
+        <v>-0.2157145414444646</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.03660468081897447</v>
+        <v>-0.05368933353243571</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.001396334884416958</v>
+        <v>0.0006488956690884453</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.06927948090771309</v>
+        <v>0.06979590523105909</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
@@ -5519,25 +5519,25 @@
         <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.05770982630329355</v>
+        <v>-0.02077349225618502</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.07097593721359893</v>
+        <v>-0.04588211495268259</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -5546,78 +5546,78 @@
         <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0947945928476534</v>
+        <v>0.0366693513914572</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.000195628065974</v>
+        <v>-0.3005794428041597</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3546461735666924</v>
+        <v>0.07115458593468207</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2140097108074146</v>
+        <v>-0.01437181680223647</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.8638897025205584</v>
+        <v>-0.4060575162893224</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4710572739720745</v>
+        <v>0.07334949511564423</v>
       </c>
       <c r="O10" t="n">
         <v>-0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.09406387604987888</v>
+        <v>-0.01701498298800208</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4102473340757384</v>
+        <v>-0.03108287433694841</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.08455032768411598</v>
+        <v>0.2784496260968693</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -5629,40 +5629,40 @@
         <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.07773832471820794</v>
+        <v>-0.06057259024711637</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.187361699922981</v>
+        <v>-0.07133657480888045</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1162275197873491</v>
+        <v>0.2485611248845102</v>
       </c>
       <c r="AG10" t="n">
         <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1937294037235946</v>
+        <v>-0.01859233003383423</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.1799235530409693</v>
+        <v>-0.1998057208374013</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -5671,25 +5671,25 @@
         <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.169663310111013</v>
+        <v>0.1921438729106745</v>
       </c>
       <c r="AP10" t="n">
         <v>-0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>-0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0.03076636276406243</v>
+        <v>-0.001128035503456145</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.8367069858023117</v>
+        <v>-0.4778452477645736</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.2553197343304497</v>
+        <v>0.2605177747588979</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,16 +5707,16 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB10" t="n">
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.01270050177357987</v>
+        <v>-0.08672499246136987</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.1918695433854889</v>
+        <v>-0.07612312968538715</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
@@ -5725,25 +5725,25 @@
         <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.2819430153610332</v>
+        <v>-0.07812507873405412</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0.1704697310074596</v>
+        <v>0.1014571317402991</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.1308766487073237</v>
+        <v>-0.127827653956172</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.2914520221573327</v>
+        <v>-0.2728031539255883</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
@@ -5767,37 +5767,37 @@
         <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.02418006514279095</v>
+        <v>-0.02460806894077286</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.5775079896191259</v>
+        <v>-0.2120907208069209</v>
       </c>
       <c r="BW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.2361855416007207</v>
+        <v>0.2057282513117803</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA10" t="n">
         <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.007939602367271764</v>
+        <v>-0.01440326815744891</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.200829888847042</v>
+        <v>0.08488801375693675</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,10 +5806,10 @@
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.06912822949654562</v>
+        <v>-0.05792730885907588</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
@@ -5821,19 +5821,19 @@
         <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.2108073509479043</v>
+        <v>0.1582802427007775</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.02698993975591833</v>
+        <v>0.1764098129773055</v>
       </c>
       <c r="CO10" t="n">
         <v>0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.6246747807104319</v>
+        <v>-0.06235595580969199</v>
       </c>
       <c r="CR10" t="n">
         <v>0</v>
@@ -5848,19 +5848,19 @@
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0.01393319264323321</v>
+        <v>-0.002091825322826272</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1926835228209358</v>
+        <v>0.08313715333916009</v>
       </c>
       <c r="CX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY10" t="n">
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.005862315482838054</v>
+        <v>-0.03581984882764026</v>
       </c>
       <c r="DA10" t="n">
         <v>-0</v>
@@ -5875,22 +5875,22 @@
         <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1717226490935927</v>
+        <v>0.02988322751472722</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.4403637173219805</v>
+        <v>0.03524781607179536</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.06150967775170918</v>
+        <v>0.001189904406566586</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
@@ -5899,49 +5899,49 @@
         <v>-0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.004834694215334534</v>
+        <v>0.02148757772044754</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.06660908990369091</v>
+        <v>0.1219976795149675</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1708401270488526</v>
+        <v>0.07366899060880708</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.01151536005050363</v>
+        <v>0.02783711235857732</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.480432641099542</v>
+        <v>0.2418560028765334</v>
       </c>
       <c r="DY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ10" t="n">
         <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.2824317113323264</v>
+        <v>0.2917503098938448</v>
       </c>
       <c r="EB10" t="n">
         <v>-0</v>
@@ -5956,10 +5956,10 @@
         <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.06467640917304741</v>
+        <v>0.01634331829605451</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.06654407801499847</v>
+        <v>0.01245265713428991</v>
       </c>
       <c r="EH10" t="n">
         <v>0</v>
@@ -5968,61 +5968,61 @@
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.220245226976764</v>
+        <v>0.006707369602653321</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
         <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.01705313109458252</v>
+        <v>-0.01948318184423935</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.08831876030190038</v>
+        <v>0.01318184335667505</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.1443800731181142</v>
+        <v>-0.01244106220295528</v>
       </c>
       <c r="ET10" t="n">
         <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.01347628540249116</v>
+        <v>-0.01128505243266603</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.2026402362596129</v>
+        <v>0.09717323786107294</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02555343966385302</v>
+        <v>-0.03047027330870004</v>
       </c>
       <c r="FC10" t="n">
         <v>0</v>
@@ -6034,49 +6034,49 @@
         <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0.01351098137261296</v>
+        <v>0.01857439141760082</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.1285620807148873</v>
+        <v>0.1803427191228496</v>
       </c>
       <c r="FI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.1676964443625349</v>
+        <v>0.1213000837143632</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0.001393995022686104</v>
+        <v>-0.001735311551240222</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.04203717078401836</v>
+        <v>-0.00285211470412785</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.05112155929047651</v>
+        <v>-0.05123063361373829</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6088,25 +6088,25 @@
         <v>-0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.1981716220921718</v>
+        <v>0.04691699275809349</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.08891479033184367</v>
+        <v>0.04084432979825237</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC10" t="n">
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE10" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5025994176302351</v>
+        <v>0.3545828212686763</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.03234233613095101</v>
+        <v>-0.1991372222818531</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -6144,13 +6144,13 @@
         <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3243190074281432</v>
+        <v>-0.07419528011378325</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3543559262263809</v>
+        <v>0.5317029307753016</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,79 +6159,79 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0727056060268471</v>
+        <v>-0.2997101625788739</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.2544294435558138</v>
+        <v>-0.1087512605346057</v>
       </c>
       <c r="S11" t="n">
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1131928689981723</v>
+        <v>0.02708640547414473</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.006154694897210576</v>
+        <v>-0.1083912036825737</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>-0.07613652471431498</v>
+        <v>-0.01983309517795192</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1703138451986171</v>
+        <v>-0.01383370403387296</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.04153114115060682</v>
+        <v>-0.1039956246144523</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.02424773754708348</v>
+        <v>0.008421021044543406</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.09552635091293049</v>
+        <v>0.1370047909112817</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,52 +6240,52 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0005930179846301423</v>
+        <v>-0.02358799507556461</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>-0.07882455555996977</v>
+        <v>0.02203366721596657</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4523337567415014</v>
+        <v>0.4707223109756103</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1517605598065375</v>
+        <v>-0.1740839964733349</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0.1404093262725181</v>
+        <v>0.01019495527010819</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.07501628806493117</v>
+        <v>-0.04270679360592765</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,25 +6294,25 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1799295426076874</v>
+        <v>-0.07260411051813248</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0.17491429587882</v>
+        <v>-0.05963286244787001</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01855901654884917</v>
+        <v>0.09122587435082521</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,52 +6321,52 @@
         <v>0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.15363148965093</v>
+        <v>0.1283736531319084</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0.01282564579733253</v>
+        <v>0.0404346239193179</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2584867140468766</v>
+        <v>0.3065848694895895</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.06779278497354253</v>
+        <v>-0.1499550881630424</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0.05439368754766404</v>
+        <v>-0.04060977199928734</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1063051417888271</v>
+        <v>-0.1412784218516184</v>
       </c>
       <c r="CF11" t="n">
         <v>-0</v>
@@ -6375,37 +6375,37 @@
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.0123999375250363</v>
+        <v>0.05352478956169792</v>
       </c>
       <c r="CI11" t="n">
         <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.08241951422047439</v>
+        <v>0.02610441452158619</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.06478893541454656</v>
+        <v>-0.2385129047129514</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.04621327902943281</v>
+        <v>0.02715975222447897</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
@@ -6414,40 +6414,40 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>-0.02343245301141927</v>
+        <v>-0.004458144553206122</v>
       </c>
       <c r="CV11" t="n">
         <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.09414416943103228</v>
+        <v>-0.1312277601510701</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.01914849684373003</v>
+        <v>0.02975361429624733</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.07504276223898444</v>
+        <v>0.02891599637899607</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.1182261744395655</v>
+        <v>-0.02961034249346532</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,7 +6456,7 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05412685565158881</v>
+        <v>-0.1041828483442449</v>
       </c>
       <c r="DJ11" t="n">
         <v>-0</v>
@@ -6468,121 +6468,121 @@
         <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.03219904337586417</v>
+        <v>-0.07614706244463255</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01423163962202957</v>
+        <v>-0.08493573190070969</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.006994885417896802</v>
+        <v>0.001160407161428532</v>
       </c>
       <c r="DS11" t="n">
         <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>-0.02374782169982614</v>
+        <v>-0.01407654548936669</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.07353167572043219</v>
+        <v>0.08934021868537179</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.04227195418086139</v>
+        <v>0.009800844020228808</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
         <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.02796226645634012</v>
+        <v>0.05777962240642723</v>
       </c>
       <c r="EF11" t="n">
         <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.03077529897577023</v>
+        <v>-0.0401055623449924</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>-0.0004336784504817793</v>
+        <v>-0.01607858878486162</v>
       </c>
       <c r="EK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.1036915773196381</v>
+        <v>0.01758761521123939</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1056797150948331</v>
+        <v>-0.05795361737981648</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.03259428197368409</v>
+        <v>0.009872192204333264</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0.04756516615355748</v>
+        <v>0.06013705484805655</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1178670650332119</v>
+        <v>-0.1606725163840855</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,25 +6591,25 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.02715481701731032</v>
+        <v>0.02255678963357994</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0646619709015803</v>
+        <v>0.03855766347935955</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.06191831366897853</v>
+        <v>-0.08349358399901825</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,7 +6618,7 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.055576272012112</v>
+        <v>0.09201888681952491</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
@@ -6630,40 +6630,40 @@
         <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.02139657467474632</v>
+        <v>0.0642152391244718</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.00148086181662483</v>
+        <v>-0.002262050785536415</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.000504162863575076</v>
+        <v>0.002046802179052992</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.01357506348458504</v>
+        <v>-0.00094535526774349</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05419168035346556</v>
+        <v>-0.04100032024613815</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6672,27 +6672,27 @@
         <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.005116448674482819</v>
+        <v>0.06198528855676559</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.1450283934898477</v>
+        <v>-0.02372056941707217</v>
       </c>
       <c r="B12" t="n">
-        <v>0.3062561047424777</v>
+        <v>0.04131643732160385</v>
       </c>
       <c r="C12" t="n">
         <v>-0</v>
@@ -6701,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004364620054611141</v>
+        <v>-0.02162038146857253</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6710,16 +6710,16 @@
         <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1332743239940226</v>
+        <v>-0.01825916109202654</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2873678197897083</v>
+        <v>0.06852518384885566</v>
       </c>
       <c r="L12" t="n">
         <v>-0</v>
@@ -6728,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.08368245261017246</v>
+        <v>-0.02477424798838624</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6743,25 +6743,25 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.005902332190468476</v>
+        <v>0.005536596808011051</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1031246008266935</v>
+        <v>0.01158359640925321</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05699720229877055</v>
+        <v>-0.001027120168831855</v>
       </c>
       <c r="X12" t="n">
         <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -6770,52 +6770,52 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.02586191543692579</v>
+        <v>0.002113451911267596</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1138783956977097</v>
+        <v>-0.00432959099537644</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.01371311578678623</v>
+        <v>-0.004875089248281705</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0.01677649799122805</v>
+        <v>0.0002488613279908987</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07775943758745023</v>
+        <v>0.01269946676217871</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.05098910888926177</v>
+        <v>-0.007202944514552173</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,37 +6824,37 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0.0239761537076614</v>
+        <v>-0.006753489854071193</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2680415258520715</v>
+        <v>0.03777836907702553</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.2275944397392204</v>
+        <v>-0.02405494863417618</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0.06963962924390511</v>
+        <v>-0.01696380532700793</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01245205525493021</v>
+        <v>0.008083584745928411</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1533763950412602</v>
+        <v>-0.01641288060446598</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0.06101163327465105</v>
+        <v>-0.001556419968043042</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.02274610606011445</v>
+        <v>0.01139177698831306</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01391576317500381</v>
+        <v>0.03067270109513913</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6905,25 +6905,25 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.01501444647920728</v>
+        <v>0.005778395511794299</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1683472121580763</v>
+        <v>0.03486235087994485</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0507792668290547</v>
+        <v>-0.008083963932858986</v>
       </c>
       <c r="BZ12" t="n">
         <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
@@ -6932,19 +6932,19 @@
         <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.04000007307173718</v>
+        <v>0.00846789383597101</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05453818036973004</v>
+        <v>-0.01321815831414361</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.03840247409659924</v>
+        <v>0.007228785096199225</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6959,10 +6959,10 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>-0.03781898321579104</v>
+        <v>-0.002237155044846617</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01379031628086412</v>
+        <v>-0.03146331233344878</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
@@ -6971,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1213706244010509</v>
+        <v>0.0173253199075242</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6986,19 +6986,19 @@
         <v>0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.02352082975433117</v>
+        <v>0.007046897657787903</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.06245390504132654</v>
+        <v>-0.01393856912233623</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02894768230131029</v>
+        <v>0.003075994520562241</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7013,19 +7013,19 @@
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.03547785053168344</v>
+        <v>0.005639751979740029</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.09648272798232696</v>
+        <v>-0.03194025957013532</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.007177448380538715</v>
+        <v>0.0002073957861581678</v>
       </c>
       <c r="DJ12" t="n">
         <v>0</v>
@@ -7034,16 +7034,16 @@
         <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.02277124310493113</v>
+        <v>0.003302379888104384</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.0129358505656151</v>
+        <v>-0.009453250971730776</v>
       </c>
       <c r="DP12" t="n">
         <v>-0</v>
@@ -7052,7 +7052,7 @@
         <v>-0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.04261667835639647</v>
+        <v>-0.009034407493439462</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
@@ -7064,13 +7064,13 @@
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.01520493498490725</v>
+        <v>0.007143814600959794</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0593548273950997</v>
+        <v>0.01605696866330404</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
@@ -7079,25 +7079,25 @@
         <v>0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01296338099423119</v>
+        <v>-0.003915224126056376</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0.01039572169350779</v>
+        <v>-0.001743608811522281</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.001263226131389152</v>
+        <v>-0.002427774456461721</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.02461621833527135</v>
+        <v>0.0008238929763544519</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,16 +7115,16 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.0106854152706513</v>
+        <v>0.00199075505787367</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.1025026239040847</v>
+        <v>0.003082732789867499</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
@@ -7133,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.03902147905849932</v>
+        <v>-0.00755196132686958</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
@@ -7142,16 +7142,16 @@
         <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.02330788700807145</v>
+        <v>0.009125890362272611</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0744448865289912</v>
+        <v>-0.01738714511535258</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
@@ -7160,7 +7160,7 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.06868372175746276</v>
+        <v>0.002798290972606765</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7175,22 +7175,22 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.02140080285614447</v>
+        <v>0.004204356067796225</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.004955464002654584</v>
+        <v>-0.009197972184496719</v>
       </c>
       <c r="FI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ12" t="n">
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.06706801856876159</v>
+        <v>0.0199435895328564</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
@@ -7202,49 +7202,49 @@
         <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.0864534031141376</v>
+        <v>0.003260733313313482</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.02326556006440409</v>
+        <v>0.001008745442009065</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.004870107481667689</v>
+        <v>0.002357171552738183</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0.0320186217691341</v>
+        <v>0.01090995520939297</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.0175993094740689</v>
+        <v>-0.01104206562405361</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,49 +7261,49 @@
         <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5070684835287268</v>
+        <v>0.1498876840207892</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1519953215431933</v>
+        <v>-0.1364141933736148</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1769548735060516</v>
+        <v>-0.0181631556956894</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3430387183262252</v>
+        <v>0.2064975568254803</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1549731854593712</v>
+        <v>-0.2092378522263859</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2009485741394578</v>
+        <v>-0.04940106228036183</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -7315,22 +7315,22 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1369897935913975</v>
+        <v>0.07079550449098998</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.125510729472762</v>
+        <v>-0.009205968607524101</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.01312121145246103</v>
+        <v>0.01523740754668955</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
@@ -7342,34 +7342,34 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1394273036977619</v>
+        <v>-0.02784208910394309</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>-0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.06253247594811912</v>
+        <v>-0.08371206247206253</v>
       </c>
       <c r="AG13" t="n">
         <v>-0</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.02575009079944633</v>
+        <v>0.02193226356156847</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04822317261119883</v>
+        <v>0.07053153116675775</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
@@ -7378,25 +7378,25 @@
         <v>-0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.008666941256081645</v>
+        <v>0.01135144812868481</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.03495606889012583</v>
+        <v>-0.01091747899311669</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4414688501999068</v>
+        <v>0.21319796836691</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,52 +7405,52 @@
         <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.03498103781186453</v>
+        <v>-0.05404260259631689</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.122386106171035</v>
+        <v>-0.01071582486017519</v>
       </c>
       <c r="BA13" t="n">
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
         <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.100733676612333</v>
+        <v>-0.06424938677928504</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.05150113679389452</v>
+        <v>-0.05385332686866674</v>
       </c>
       <c r="BH13" t="n">
         <v>-0</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0.08747455111042932</v>
+        <v>-0.02175083034753827</v>
       </c>
       <c r="BJ13" t="n">
         <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03325863507546089</v>
+        <v>0.01816080407422527</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,67 +7459,67 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.1244404288640718</v>
+        <v>0.09600022582213363</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0.03947354190521901</v>
+        <v>0.03629434371017379</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2018127536076341</v>
+        <v>0.1972814618110984</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.01139150127486592</v>
+        <v>-0.02892477512729887</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
-        <v>-0.06301471481279776</v>
+        <v>0.01196444297906586</v>
       </c>
       <c r="CB13" t="n">
         <v>-0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1078788746939449</v>
+        <v>-0.07219594852030808</v>
       </c>
       <c r="CF13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.02996560589584826</v>
+        <v>0.0568909124444956</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.05319002826730744</v>
+        <v>0.002275289988846612</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
@@ -7528,25 +7528,25 @@
         <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.1078420040983675</v>
+        <v>-0.1244590333355436</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.1202469607854581</v>
+        <v>0.01769701983596822</v>
       </c>
       <c r="CR13" t="n">
         <v>0</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.02886145479119778</v>
+        <v>0.0008410263261037112</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7555,10 +7555,10 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.09029384795738359</v>
+        <v>-0.06549972757007869</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,13 +7567,13 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.02866149027583024</v>
+        <v>0.05196406970298974</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.03656536726165375</v>
+        <v>0.01558049705673411</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
@@ -7582,28 +7582,28 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.2628776269842755</v>
+        <v>-0.09255226131075805</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.04319878717753253</v>
+        <v>-0.01761381686275465</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
       </c>
       <c r="DK13" t="n">
-        <v>-0.05513804135011058</v>
+        <v>-0.02782012491677582</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>-0</v>
@@ -7612,7 +7612,7 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03104925690354835</v>
+        <v>-0.02675991577104927</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
@@ -7621,40 +7621,40 @@
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.007103100026380021</v>
+        <v>0.0563234503730474</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.02356251419881231</v>
+        <v>0.01657187547259482</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.09428272573595585</v>
+        <v>0.05413266715387655</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.06232901063393878</v>
+        <v>-0.05352780952281946</v>
       </c>
       <c r="EB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC13" t="n">
-        <v>-0.02341972319180255</v>
+        <v>-0.009665169472749882</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
@@ -7663,25 +7663,25 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.07880185137472134</v>
+        <v>-0.03050618124029291</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.05017273052686625</v>
+        <v>0.023933419586733</v>
       </c>
       <c r="EK13" t="n">
         <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.04341235960728476</v>
+        <v>-0.01143996112028552</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
@@ -7690,10 +7690,10 @@
         <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03067011551221096</v>
+        <v>-0.04836572236002094</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,25 +7702,25 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0853738739473147</v>
+        <v>-0.006764729506276938</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0.03959466301732154</v>
+        <v>0.0190347454789135</v>
       </c>
       <c r="EV13" t="n">
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.09231393266458732</v>
+        <v>-0.07537863319837283</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,13 +7729,13 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.02193125867806608</v>
+        <v>0.03977439090055263</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.03532723903125196</v>
+        <v>0.0002805137058748994</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
@@ -7747,34 +7747,34 @@
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.04400904787193322</v>
+        <v>-0.02977305192953052</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1127322733516995</v>
+        <v>-0.00238519507279046</v>
       </c>
       <c r="FL13" t="n">
         <v>-0</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.02411277505497511</v>
+        <v>-0.02780115891472282</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.009793930386886193</v>
+        <v>-0.004262832548478069</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,13 +7783,13 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.005182557770810742</v>
+        <v>-0.0006412981209867683</v>
       </c>
       <c r="FU13" t="n">
         <v>0</v>
       </c>
       <c r="FV13" t="n">
-        <v>-0.03051656735267664</v>
+        <v>-0.02823501201817321</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
@@ -7798,31 +7798,31 @@
         <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.05903719563294344</v>
+        <v>-0.04499924648852983</v>
       </c>
       <c r="GA13" t="n">
         <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.001741469352806429</v>
+        <v>-0.009704480770243513</v>
       </c>
       <c r="GF13" t="n">
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8399,22 +8399,22 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.1869573382331637</v>
+        <v>-0.3350511691159093</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3023184592343354</v>
+        <v>0.2918784289450576</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02272039432838016</v>
+        <v>0.2254039522531619</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8426,22 +8426,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1604474752503273</v>
+        <v>-0.3827618363625123</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.327655719272808</v>
+        <v>0.4739374422213596</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1113456600398723</v>
+        <v>0.2812466117708723</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -8450,73 +8450,73 @@
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.02691806874379581</v>
+        <v>-0.06079196189306236</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0143252989727879</v>
+        <v>0.05665734576829226</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1060886056445353</v>
+        <v>0.01158448582033745</v>
       </c>
       <c r="X15" t="n">
         <v>-0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.04970619789400177</v>
+        <v>-0.0431379467496141</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.03045049329929172</v>
+        <v>0.07435637498327544</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.009733480363607931</v>
+        <v>-0.06540144884474253</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.05487763676867052</v>
+        <v>-0.2044893153308514</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.01266633104407108</v>
+        <v>0.03306437972438154</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.02272793854071766</v>
+        <v>-0.2128464081588029</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
@@ -8534,43 +8534,43 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.286873477679045</v>
+        <v>-0.5129365673541126</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.006458170809651075</v>
+        <v>0.09139728839416575</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.1412027336967856</v>
+        <v>0.130562653868143</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.02976041038025856</v>
+        <v>0.09720357722809783</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.166452845645908</v>
+        <v>0.1108832940219397</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.2375478576965494</v>
+        <v>0.1868910663891738</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8579,7 +8579,7 @@
         <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
@@ -8588,25 +8588,25 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.0462724637641261</v>
+        <v>0.09804128808749345</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.03683820245122325</v>
+        <v>-0.01639128221932321</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.06523694290064841</v>
+        <v>-0.02221794239396222</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
@@ -8615,46 +8615,46 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.1781186781916282</v>
+        <v>-0.3275335354724262</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0.01236493487917666</v>
+        <v>0.1823546921406823</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.008724332733459643</v>
+        <v>0.05967607341631333</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
       </c>
       <c r="CA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.04387018383907025</v>
+        <v>0.197888492854103</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.08760037473582617</v>
+        <v>-0.09492263242996703</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.02148408688146284</v>
+        <v>-0.009942173313494781</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
         <v>0</v>
@@ -8669,19 +8669,19 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.01388834498071505</v>
+        <v>0.1979153523244146</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0.0215314864692131</v>
+        <v>-0.2525537709634357</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.008018795035296396</v>
+        <v>-0.1126649565005415</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8693,22 +8693,22 @@
         <v>0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.05158609911742962</v>
+        <v>0.1977042645155877</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.07684784951489181</v>
+        <v>-0.1054206641636186</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.001455367635933529</v>
+        <v>-0.03037319858350699</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB15" t="n">
         <v>-0</v>
@@ -8720,22 +8720,22 @@
         <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.06348848124026969</v>
+        <v>0.04918202867661803</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.0007436809931250562</v>
+        <v>-0.1105866557255497</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.04827039199911155</v>
+        <v>0.01849438182172237</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8747,28 +8747,28 @@
         <v>-0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.03755457765395096</v>
+        <v>0.0748858532914841</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.1080578250472073</v>
+        <v>-0.05749779092765403</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.02462519411844031</v>
+        <v>0.07931142132178826</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,52 +8777,52 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.002575986165579502</v>
+        <v>-0.06854441440130991</v>
       </c>
       <c r="DY15" t="n">
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.01733143302964566</v>
+        <v>-0.06773619744201057</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.01297561302774764</v>
+        <v>-0.007867880610552883</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-1.661808614858435e-05</v>
+        <v>0.2006469187917476</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.03391516116037453</v>
+        <v>-0.03356676119331643</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.02492316413475851</v>
+        <v>-0.06021994674353744</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL15" t="n">
         <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>0</v>
@@ -8831,46 +8831,46 @@
         <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.05047716562235082</v>
+        <v>0.1135436331762059</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0.08673432366434224</v>
+        <v>-0.05986646333385267</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.1004827382937108</v>
+        <v>-0.03244833617190705</v>
       </c>
       <c r="ET15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
         <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.06283022070518648</v>
+        <v>0.2344171159129403</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.08369018873682219</v>
+        <v>-0.1297286575581099</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.02190161719298093</v>
+        <v>-0.03411389058439795</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
@@ -8882,46 +8882,46 @@
         <v>0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.05941678116704303</v>
+        <v>0.1123909793276081</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.01588095675096045</v>
+        <v>0.07844988951381356</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.04108164447852088</v>
+        <v>-0.01751930145807183</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
         <v>0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.00230800481226204</v>
+        <v>0.1427183356207509</v>
       </c>
       <c r="FR15" t="n">
         <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0.04876600872004058</v>
+        <v>-0.07314472079688968</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.02332196084833215</v>
+        <v>-0.01213214324558594</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
@@ -8930,22 +8930,22 @@
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.07653023830897418</v>
+        <v>0.1669041671890789</v>
       </c>
       <c r="GA15" t="n">
         <v>-0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.1406764507148384</v>
+        <v>-0.03916270300614899</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
@@ -8960,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
